--- a/Data/EXCEL/Transfer/bzPerformance/2024Q4/2761-bzPerformance-2024Q4.xlsx
+++ b/Data/EXCEL/Transfer/bzPerformance/2024Q4/2761-bzPerformance-2024Q4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\xls2xlsx\2024Q4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{480BC6F7-E0C1-4D35-8D80-5810FC02FB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F99C88E9-9DFD-470B-AB52-5A366BC79740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1800" yWindow="840" windowWidth="17640" windowHeight="14310" xr2:uid="{FD921535-EA32-4A7C-A234-C2CC067F8264}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{76028952-99F1-4FB6-BB5D-7DD4187531D4}"/>
   </bookViews>
   <sheets>
     <sheet name="2761-bzPerformance-2024Q4" sheetId="2" r:id="rId1"/>
@@ -305,14 +305,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="1"/>
@@ -322,6 +314,14 @@
     <font>
       <sz val="8"/>
       <color rgb="FF808080"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="1"/>
       <charset val="136"/>
@@ -895,7 +895,10 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -904,15 +907,12 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -943,10 +943,10 @@
     <xf numFmtId="0" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1323,14 +1323,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D95E44D3-DEA3-48B5-BD58-9C5EEAC1C46F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCA74649-5074-44C1-B25C-387EE5AC1D96}">
   <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="17" width="7.08984375" customWidth="1"/>
-    <col min="18" max="18" width="7.36328125" customWidth="1"/>
-    <col min="19" max="20" width="7.08984375" customWidth="1"/>
-    <col min="21" max="21" width="8.90625" customWidth="1"/>
+    <col min="1" max="17" width="11.6328125" customWidth="1"/>
+    <col min="18" max="18" width="12.08984375" customWidth="1"/>
+    <col min="19" max="20" width="11.6328125" customWidth="1"/>
+    <col min="21" max="21" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="1" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
@@ -1497,16 +1497,16 @@
         <v>27</v>
       </c>
       <c r="D4" s="7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4" s="7">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="F4" s="8">
-        <v>0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="G4" s="8">
-        <v>0.7</v>
+        <v>-2.8</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>27</v>
@@ -1659,10 +1659,10 @@
       <c r="E7" s="7">
         <v>59.4</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="12">
         <v>14.5</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="12">
         <v>35.200000000000003</v>
       </c>
       <c r="H7" s="7">
@@ -1701,7 +1701,7 @@
       <c r="S7" s="7">
         <v>1.2</v>
       </c>
-      <c r="T7" s="8">
+      <c r="T7" s="12">
         <v>0.4</v>
       </c>
       <c r="U7" s="7">
@@ -1709,67 +1709,67 @@
       </c>
     </row>
     <row r="8" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A8" s="12">
+      <c r="A8" s="13">
         <v>2022</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="14">
         <v>1.41</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="14">
         <v>55</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="14">
         <v>41.2</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="14">
         <v>42.5</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="15">
         <v>-15.7</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="15">
         <v>-27.6</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="14">
         <v>6.81</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="14">
         <v>3.16</v>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="14">
         <v>0</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="14">
         <v>0.15</v>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="14">
         <v>0.11</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="14">
         <v>46.4</v>
       </c>
-      <c r="N8" s="13">
+      <c r="N8" s="14">
         <v>0.03</v>
       </c>
-      <c r="O8" s="13">
+      <c r="O8" s="14">
         <v>2.2400000000000002</v>
       </c>
-      <c r="P8" s="13">
+      <c r="P8" s="14">
         <v>1.86</v>
       </c>
-      <c r="Q8" s="13">
+      <c r="Q8" s="14">
         <v>4.76</v>
       </c>
-      <c r="R8" s="13">
+      <c r="R8" s="14">
         <v>2</v>
       </c>
-      <c r="S8" s="13">
+      <c r="S8" s="14">
         <v>0.8</v>
       </c>
-      <c r="T8" s="14">
+      <c r="T8" s="15">
         <v>-0.01</v>
       </c>
-      <c r="U8" s="13">
+      <c r="U8" s="14">
         <v>21.56</v>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       <c r="S9" s="7">
         <v>0.81</v>
       </c>
-      <c r="T9" s="15">
+      <c r="T9" s="8">
         <v>-1.19</v>
       </c>
       <c r="U9" s="7">
@@ -1839,67 +1839,67 @@
       </c>
     </row>
     <row r="10" spans="1:21" s="9" customFormat="1" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A10" s="12">
+      <c r="A10" s="13">
         <v>2020</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="14">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="14">
         <v>53</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="13">
+      <c r="D10" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="14">
         <v>6.82</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="14">
         <v>3.38</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="14">
         <v>0.33</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10" s="15">
         <v>-0.06</v>
       </c>
-      <c r="L10" s="13">
+      <c r="L10" s="14">
         <v>0.23</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="14">
         <v>49.6</v>
       </c>
-      <c r="N10" s="13">
+      <c r="N10" s="14">
         <v>4.8499999999999996</v>
       </c>
-      <c r="O10" s="14">
+      <c r="O10" s="15">
         <v>-0.93</v>
       </c>
-      <c r="P10" s="13">
+      <c r="P10" s="14">
         <v>3.61</v>
       </c>
-      <c r="Q10" s="13">
+      <c r="Q10" s="14">
         <v>12.1</v>
       </c>
-      <c r="R10" s="13">
+      <c r="R10" s="14">
         <v>4.5</v>
       </c>
-      <c r="S10" s="13">
+      <c r="S10" s="14">
         <v>2</v>
       </c>
       <c r="T10" s="16">
         <v>2.5099999999999998</v>
       </c>
-      <c r="U10" s="12" t="s">
+      <c r="U10" s="13" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1934,10 +1934,10 @@
       <c r="J11" s="7">
         <v>0.11</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="8">
         <v>-0.16</v>
       </c>
-      <c r="L11" s="15">
+      <c r="L11" s="8">
         <v>-0.06</v>
       </c>
       <c r="M11" s="7">
@@ -1946,19 +1946,19 @@
       <c r="N11" s="7">
         <v>1.51</v>
       </c>
-      <c r="O11" s="15">
+      <c r="O11" s="8">
         <v>-2.27</v>
       </c>
-      <c r="P11" s="15">
+      <c r="P11" s="8">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="Q11" s="15">
+      <c r="Q11" s="8">
         <v>-4.13</v>
       </c>
-      <c r="R11" s="15">
+      <c r="R11" s="8">
         <v>-1.4</v>
       </c>
-      <c r="S11" s="15">
+      <c r="S11" s="8">
         <v>-0.51</v>
       </c>
       <c r="T11" s="6" t="s">
